--- a/data/trans_bre/IP16B05-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16B05-Estudios-trans_bre.xlsx
@@ -714,12 +714,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-42,31; 0,0</t>
+          <t>-41,44; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,03</t>
+          <t>0,0; 26,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-42,31; 0,0</t>
+          <t>-41,44; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,03</t>
+          <t>0,0; 35,29</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 0,0</t>
+          <t>-28,27; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,7</t>
+          <t>0,0; 14,19</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-23,58; 0,0</t>
+          <t>-28,27; 0,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,04</t>
+          <t>0,0; 16,54</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">

--- a/data/trans_bre/IP16B05-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/IP16B05-Estudios-trans_bre.xlsx
@@ -714,12 +714,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-41,44; 0,0</t>
+          <t>-40,18; 0,0</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,04</t>
+          <t>0,0; 24,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -729,12 +729,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-41,44; 0,0</t>
+          <t>-40,18; 0,0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,29</t>
+          <t>0,0; 33,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -874,12 +874,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-28,27; 0,0</t>
+          <t>-28,46; 0,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,19</t>
+          <t>0,0; 17,1</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -889,12 +889,12 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-28,27; 0,0</t>
+          <t>-28,46; 0,0</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,54</t>
+          <t>0,0; 20,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
